--- a/outputs/59794.xlsx
+++ b/outputs/59794.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
   <si>
     <t xml:space="preserve">EXAMPLE OF WHAT WHAT INFORMATION I CURRENTLY HAVE*</t>
   </si>
@@ -58,19 +58,49 @@
     <t xml:space="preserve">Column9</t>
   </si>
   <si>
-    <t xml:space="preserve">Column10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column11</t>
-  </si>
-  <si>
     <t xml:space="preserve">WORD1XXXX/WORD2/WORD3/WORD4/-/-/WORD5/WORD6XX/-/-/2019 - 2020</t>
   </si>
   <si>
+    <t xml:space="preserve">WORD1XXXX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WORD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WORD3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WORD4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WORD5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WORD6XX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019 - 2020</t>
+  </si>
+  <si>
     <t xml:space="preserve">WORD1XXXX/WORD2/WORD3XXX/WORD4/-/-/WORD5/WORD6/-/-/2019 - 2020</t>
   </si>
   <si>
+    <t xml:space="preserve">WORD3XXX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WORD6</t>
+  </si>
+  <si>
     <t xml:space="preserve">WORD1/WORD2/WORD3/WORD4/-/-/WORD5XXX/WORD6/-/-/2019 - 2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WORD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WORD5XXX</t>
   </si>
 </sst>
 </file>
@@ -172,39 +202,39 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -520,158 +550,119 @@
       <c r="K2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A3,"/",REPT(" ",100)),(1-1)*100+1,100))</f>
-        <v>WORD1XXXX</v>
-      </c>
-      <c r="D3" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A3,"/",REPT(" ",100)),(2-1)*100+1,100))</f>
-        <v>WORD2</v>
-      </c>
-      <c r="E3" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A3,"/",REPT(" ",100)),(3-1)*100+1,100))</f>
-        <v>WORD3</v>
-      </c>
-      <c r="F3" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A3,"/",REPT(" ",100)),(4-1)*100+1,100))</f>
-        <v>WORD4</v>
-      </c>
-      <c r="G3" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A3,"/",REPT(" ",100)),(5-1)*100+1,100))</f>
-        <v>-</v>
-      </c>
-      <c r="H3" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A3,"/",REPT(" ",100)),(6-1)*100+1,100))</f>
-        <v>-</v>
-      </c>
-      <c r="I3" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A3,"/",REPT(" ",100)),(7-1)*100+1,100))</f>
-        <v>WORD5</v>
-      </c>
-      <c r="J3" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A3,"/",REPT(" ",100)),(8-1)*100+1,100))</f>
-        <v>WORD6XX</v>
-      </c>
-      <c r="K3" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A3,"/",REPT(" ",100)),(9-1)*100+1,100))</f>
-        <v>-</v>
-      </c>
-      <c r="L3" s="8" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A3,"/",REPT(" ",100)),(10-1)*100+1,100))</f>
-        <v>-</v>
-      </c>
-      <c r="M3" s="8" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A3,"/",REPT(" ",100)),(11-1)*100+1,100))</f>
-        <v>2019 - 2020</v>
+      <c r="E3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A4,"/",REPT(" ",100)),(1-1)*100+1,100))</f>
-        <v>WORD1XXXX</v>
-      </c>
-      <c r="D4" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A4,"/",REPT(" ",100)),(2-1)*100+1,100))</f>
-        <v>WORD2</v>
-      </c>
-      <c r="E4" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A4,"/",REPT(" ",100)),(3-1)*100+1,100))</f>
-        <v>WORD3XXX</v>
-      </c>
-      <c r="F4" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A4,"/",REPT(" ",100)),(4-1)*100+1,100))</f>
-        <v>WORD4</v>
-      </c>
-      <c r="G4" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A4,"/",REPT(" ",100)),(5-1)*100+1,100))</f>
-        <v>-</v>
-      </c>
-      <c r="H4" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A4,"/",REPT(" ",100)),(6-1)*100+1,100))</f>
-        <v>-</v>
-      </c>
-      <c r="I4" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A4,"/",REPT(" ",100)),(7-1)*100+1,100))</f>
-        <v>WORD5</v>
-      </c>
-      <c r="J4" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A4,"/",REPT(" ",100)),(8-1)*100+1,100))</f>
-        <v>WORD6</v>
-      </c>
-      <c r="K4" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A4,"/",REPT(" ",100)),(9-1)*100+1,100))</f>
-        <v>-</v>
-      </c>
-      <c r="L4" s="8" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A4,"/",REPT(" ",100)),(10-1)*100+1,100))</f>
-        <v>-</v>
-      </c>
-      <c r="M4" s="8" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A4,"/",REPT(" ",100)),(11-1)*100+1,100))</f>
-        <v>2019 - 2020</v>
+        <v>21</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A5,"/",REPT(" ",100)),(1-1)*100+1,100))</f>
-        <v>WORD1</v>
-      </c>
-      <c r="D5" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A5,"/",REPT(" ",100)),(2-1)*100+1,100))</f>
-        <v>WORD2</v>
-      </c>
-      <c r="E5" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A5,"/",REPT(" ",100)),(3-1)*100+1,100))</f>
-        <v>WORD3</v>
-      </c>
-      <c r="F5" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A5,"/",REPT(" ",100)),(4-1)*100+1,100))</f>
-        <v>WORD4</v>
-      </c>
-      <c r="G5" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A5,"/",REPT(" ",100)),(5-1)*100+1,100))</f>
-        <v>-</v>
-      </c>
-      <c r="H5" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A5,"/",REPT(" ",100)),(6-1)*100+1,100))</f>
-        <v>-</v>
-      </c>
-      <c r="I5" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A5,"/",REPT(" ",100)),(7-1)*100+1,100))</f>
-        <v>WORD5XXX</v>
-      </c>
-      <c r="J5" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A5,"/",REPT(" ",100)),(8-1)*100+1,100))</f>
-        <v>WORD6</v>
-      </c>
-      <c r="K5" s="7" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A5,"/",REPT(" ",100)),(9-1)*100+1,100))</f>
-        <v>-</v>
-      </c>
-      <c r="L5" s="8" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A5,"/",REPT(" ",100)),(10-1)*100+1,100))</f>
-        <v>-</v>
-      </c>
-      <c r="M5" s="8" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE($A5,"/",REPT(" ",100)),(11-1)*100+1,100))</f>
-        <v>2019 - 2020</v>
+      <c r="G5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
